--- a/data/imports/visited-places.xlsx
+++ b/data/imports/visited-places.xlsx
@@ -339,7 +339,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z98"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -1531,14 +1531,38 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="0" t="inlineStr">
         <is>
           <t>משק בגבעה גדרה</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>מרכז</t>
+      <c r="B98" s="0" t="inlineStr">
+        <is>
+          <t>מרכז</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="inlineStr">
+        <is>
+          <t>פארק אוטופיה</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="inlineStr">
+        <is>
+          <t>השרון</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>בלאגן ביגור</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>צפון</t>
         </is>
       </c>
     </row>

--- a/data/imports/visited-places.xlsx
+++ b/data/imports/visited-places.xlsx
@@ -339,7 +339,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z100"/>
+  <dimension ref="A1:Z99"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>שמורת טבע בניאס</t>
+          <t>שמורת הטבע בניאס</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>בניאס</t>
+          <t>שמורת טבע גמלא</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>שמורת טבע גמלא</t>
+          <t>יקב רמת הגולן</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -897,43 +897,43 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>יקב רמת הגולן</t>
+          <t>מעיינות גיבתון</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>צפון</t>
+          <t>מרכז</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>מעיינות גיבתון</t>
+          <t>יער צרעה</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>מרכז</t>
+          <t>ירושלים</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>יער צרעה</t>
+          <t>חוף החשמל</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>ירושלים</t>
+          <t>מרכז</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>חוף החשמל</t>
+          <t>תל גזר</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>תל גזר</t>
+          <t>פארק קנדה</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -957,19 +957,19 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>פארק קנדה</t>
+          <t>עין פאשחה עיינות צוקים</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>מרכז</t>
+          <t>דרום</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>עין פאשחה עיינות צוקים</t>
+          <t>אגם ניצנים</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -981,31 +981,31 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>אגם ניצנים</t>
+          <t>עין לבן</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>דרום</t>
+          <t>ירושלים</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>עין לבן</t>
+          <t>פארק אקולוגי הוד השרון</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>ירושלים</t>
+          <t>מרכז</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>פארק אקולוגי הוד השרון</t>
+          <t>המפל הנסתר</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -1017,7 +1017,7 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>המפל הנסתר</t>
+          <t>בית לאה</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -1029,7 +1029,7 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>בית לאה</t>
+          <t>תחנת אבו רבאח</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -1041,31 +1041,31 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>תחנת אבו רבאח</t>
+          <t>פארק לכיש</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>מרכז</t>
+          <t>דרום</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>פארק לכיש</t>
+          <t>יער המגינים</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>דרום</t>
+          <t>מרכז</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>יער המגינים</t>
+          <t>תל אפק</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -1077,19 +1077,19 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>תל אפק</t>
+          <t>מעיין חרוד</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>מרכז</t>
+          <t>צפון</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>מעיין חרוד</t>
+          <t xml:space="preserve">עין מודע </t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">עין מודע </t>
+          <t>נחל הקיבוצים</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>נחל הקיבוצים</t>
+          <t>כינרת</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -1125,7 +1125,7 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>כינרת</t>
+          <t>גני חוגה</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>גני חוגה</t>
+          <t>סכר אלומות</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -1149,7 +1149,7 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>סכר אלומות</t>
+          <t>עכו</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -1161,7 +1161,7 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>עכו</t>
+          <t>ראש הנקרה</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -1173,7 +1173,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>ראש הנקרה</t>
+          <t>עין חרדלית</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -1185,7 +1185,7 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>עין חרדלית</t>
+          <t>החוף של מוש אכזיב</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -1197,19 +1197,19 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>החוף של מוש אכזיב</t>
+          <t>קומראן</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>צפון</t>
+          <t>דרום</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>קומראן</t>
+          <t>חאן עין גדי</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -1221,7 +1221,7 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>חאן עין גדי</t>
+          <t>אמציה</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -1233,7 +1233,7 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>אמציה</t>
+          <t>יער המלאכים</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -1245,19 +1245,19 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>יער המלאכים</t>
+          <t>קלחים ומבוכים</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>דרום</t>
+          <t>מרכז</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>קלחים ומבוכים</t>
+          <t>גן לאומי מגדל צדק</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -1269,31 +1269,31 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>גן לאומי מגדל צדק</t>
+          <t>בת שלמה</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>מרכז</t>
+          <t>צפון</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>בת שלמה</t>
+          <t xml:space="preserve">טל שחר </t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>צפון</t>
+          <t>מרכז</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">טל שחר </t>
+          <t>עיזה פזיזה</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -1305,7 +1305,7 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>עיזה פזיזה</t>
+          <t xml:space="preserve">משמר דוד </t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -1317,19 +1317,19 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">משמר דוד </t>
+          <t>בית גוברין</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>מרכז</t>
+          <t>דרום</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>בית גוברין</t>
+          <t xml:space="preserve">נחל דוד </t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -1341,43 +1341,43 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">נחל דוד </t>
+          <t>מוזיאון הילדים חולון</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>דרום</t>
+          <t>מרכז</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>מוזיאון הילדים חולון</t>
+          <t>עין חמד</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>מרכז</t>
+          <t>ירושלים</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>עין חמד</t>
+          <t>נוף איילון</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>ירושלים</t>
+          <t>מרכז</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>נוף איילון</t>
+          <t>פארק בריטניה</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -1389,79 +1389,79 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>פארק בריטניה</t>
+          <t>בתרונות רוחמה</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>מרכז</t>
+          <t>דרום</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>בתרונות רוחמה</t>
+          <t>ברבטבע</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>דרום</t>
+          <t>מרכז</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>ברבטבע</t>
+          <t>רבדים</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>מרכז</t>
+          <t>דרום</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>רבדים</t>
+          <t xml:space="preserve">גבעת הרקפות </t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>דרום</t>
+          <t>מרכז</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">גבעת הרקפות </t>
+          <t>עין בוקק</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>מרכז</t>
+          <t>דרום</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>עין בוקק</t>
+          <t>עמק האלה</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>דרום</t>
+          <t>ירושלים</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>עמק האלה</t>
+          <t>מאגר בית זית</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>מאגר בית זית</t>
+          <t>הסטף</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -1485,19 +1485,19 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>הסטף</t>
+          <t>תל חדיד</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>ירושלים</t>
+          <t>מרכז</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>תל חדיד</t>
+          <t>מצפה נתן</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -1509,58 +1509,46 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>מצפה נתן</t>
+          <t>מדבריום</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>מרכז</t>
+          <t>דרום</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>מדבריום</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>דרום</t>
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t>משק בגבעה גדרה</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="inlineStr">
+        <is>
+          <t>מרכז</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t>משק בגבעה גדרה</t>
+          <t>פארק אוטופיה</t>
         </is>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>מרכז</t>
+          <t>השרון</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t>פארק אוטופיה</t>
+          <t>בלאגן ביגור</t>
         </is>
       </c>
       <c r="B99" s="0" t="inlineStr">
-        <is>
-          <t>השרון</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>בלאגן ביגור</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
         <is>
           <t>צפון</t>
         </is>
